--- a/Challenge_2_House_Price/process/exps/record.xlsx
+++ b/Challenge_2_House_Price/process/exps/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dai_hoc\nam3\HK5\ML\LAB_GROUP\Challenge_2_House_Price\process\exps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE6AC00B-BA47-4823-AE8D-AEB26FEA01ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A933C756-1CB6-4B83-B845-E9491994E0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="03-11-2025" sheetId="1" r:id="rId1"/>
@@ -694,9 +694,6 @@
     <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="15"/>
       <c r="B8" s="16"/>
-      <c r="D8" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
@@ -704,9 +701,6 @@
       </c>
       <c r="B9" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="D9" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -962,10 +956,16 @@
     <row r="8" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11"/>
       <c r="B8" s="12"/>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
       <c r="H9" s="10"/>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
